--- a/Copper/6. Sensitivity analyses/Plots of HA SA/HA_Sensitivity_Summary.xlsx
+++ b/Copper/6. Sensitivity analyses/Plots of HA SA/HA_Sensitivity_Summary.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t xml:space="preserve">Typology</t>
   </si>
@@ -58,12 +58,6 @@
   </si>
   <si>
     <t xml:space="preserve">50-60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60-70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70-80</t>
   </si>
   <si>
     <t xml:space="preserve">NP Tribs</t>
@@ -577,86 +571,86 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.00000000160569786788999</v>
+        <v>-0.00000000431212662469429</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000000000262435774373832</v>
+        <v>0.000000000732510674399534</v>
       </c>
       <c r="E7" t="n">
-        <v>-10.8467582014117</v>
+        <v>-39.2443546078952</v>
       </c>
       <c r="F7" t="n">
-        <v>0.14914553379026</v>
+        <v>0.908466087854785</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0499377048516895</v>
+        <v>-0.217024126734495</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000714250344220309</v>
+        <v>0.00633693598334707</v>
       </c>
       <c r="I7" t="n">
-        <v>127</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.00000000126886278102653</v>
+        <v>-0.00000000184125693789807</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000000000201834358210185</v>
+        <v>0.000000000298774498861813</v>
       </c>
       <c r="E8" t="n">
-        <v>-9.7720238460795</v>
+        <v>-28.1862503999904</v>
       </c>
       <c r="F8" t="n">
-        <v>0.125682346459932</v>
+        <v>0.481881337044835</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0447108124144785</v>
+        <v>-0.143917388131278</v>
       </c>
       <c r="H8" t="n">
-        <v>0.000595900941300992</v>
+        <v>0.00287786577037895</v>
       </c>
       <c r="I8" t="n">
-        <v>127</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.00000000431212662469429</v>
+        <v>-0.00000000102224736035393</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000000000732510674399534</v>
+        <v>0.000000000162168698509139</v>
       </c>
       <c r="E9" t="n">
-        <v>-39.2443546078952</v>
+        <v>-21.9860667878466</v>
       </c>
       <c r="F9" t="n">
-        <v>0.908466087854785</v>
+        <v>0.29777385282192</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.217024126734495</v>
+        <v>-0.107868538314292</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00633693598334707</v>
+        <v>0.00164514860302336</v>
       </c>
       <c r="I9" t="n">
         <v>14</v>
@@ -664,28 +658,28 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.00000000184125693789807</v>
+        <v>-0.000000000650526269084162</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000000000298774498861813</v>
+        <v>0.000000000101814451582528</v>
       </c>
       <c r="E10" t="n">
-        <v>-28.1862503999904</v>
+        <v>-18.0216151340535</v>
       </c>
       <c r="F10" t="n">
-        <v>0.481881337044835</v>
+        <v>0.202070243403988</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.143917388131278</v>
+        <v>-0.0863176783693471</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00287786577037895</v>
+        <v>0.00106509249819166</v>
       </c>
       <c r="I10" t="n">
         <v>14</v>
@@ -693,28 +687,28 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.00000000102224736035393</v>
+        <v>-0.000000000450472994053227</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000000000162168698509139</v>
+        <v>0.0000000000698706871238354</v>
       </c>
       <c r="E11" t="n">
-        <v>-21.9860667878466</v>
+        <v>-15.2693905045291</v>
       </c>
       <c r="F11" t="n">
-        <v>0.29777385282192</v>
+        <v>0.146161932400706</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.107868538314292</v>
+        <v>-0.0719680291788789</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00164514860302336</v>
+        <v>0.000746457703950461</v>
       </c>
       <c r="I11" t="n">
         <v>14</v>
@@ -722,144 +716,144 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.000000000650526269084162</v>
+        <v>-0.0000000101365266565971</v>
       </c>
       <c r="D12" t="n">
-        <v>0.000000000101814451582528</v>
+        <v>0.00000000261414290126978</v>
       </c>
       <c r="E12" t="n">
-        <v>-18.0216151340535</v>
+        <v>-31.4127567413295</v>
       </c>
       <c r="F12" t="n">
-        <v>0.202070243403988</v>
+        <v>0.478777520088047</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0863176783693471</v>
+        <v>-0.164772519519664</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00106509249819166</v>
+        <v>0.00300877299503251</v>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.000000000450472994053227</v>
+        <v>-0.00000000529431734128614</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0000000000698706871238354</v>
+        <v>0.00000000148290068883031</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.2693905045291</v>
+        <v>-23.9286150564038</v>
       </c>
       <c r="F13" t="n">
-        <v>0.146161932400706</v>
+        <v>0.285691448463723</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0719680291788789</v>
+        <v>-0.119073063016372</v>
       </c>
       <c r="H13" t="n">
-        <v>0.000746457703950461</v>
+        <v>0.00161998195318168</v>
       </c>
       <c r="I13" t="n">
-        <v>14</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.000000000330436535989546</v>
+        <v>-0.0000000032151860050683</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0000000000509237360986556</v>
+        <v>0.000000000929497879865746</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.2467156528484</v>
+        <v>-19.3165293475852</v>
       </c>
       <c r="F14" t="n">
-        <v>0.110673508789087</v>
+        <v>0.190710549440983</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0617186521199884</v>
+        <v>-0.093332301387409</v>
       </c>
       <c r="H14" t="n">
-        <v>0.000552538727642766</v>
+        <v>0.00102126338610707</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.000000000252779735760042</v>
+        <v>-0.00000000214170459450046</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0000000000387687930723166</v>
+        <v>0.000000000624174037887801</v>
       </c>
       <c r="E15" t="n">
-        <v>-11.6987825088521</v>
+        <v>-16.1925691927188</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0869515790411032</v>
+        <v>0.136803551247869</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0540360379390628</v>
+        <v>-0.0767733162364369</v>
       </c>
       <c r="H15" t="n">
-        <v>0.000426754373127797</v>
+        <v>0.000706261241767529</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0000000101365266565971</v>
+        <v>-0.00000000152126988823109</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00000000261414290126978</v>
+        <v>0.000000000442614365083958</v>
       </c>
       <c r="E16" t="n">
-        <v>-31.4127567413295</v>
+        <v>-13.9373464420318</v>
       </c>
       <c r="F16" t="n">
-        <v>0.478777520088047</v>
+        <v>0.103091800728416</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.164772519519664</v>
+        <v>-0.0652153796755085</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00300877299503251</v>
+        <v>0.000518793080148642</v>
       </c>
       <c r="I16" t="n">
         <v>98</v>
@@ -867,378 +861,146 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.00000000529431734128614</v>
+        <v>-0.00000000520693650759922</v>
       </c>
       <c r="D17" t="n">
-        <v>0.00000000148290068883031</v>
+        <v>0.00000000041839707087581</v>
       </c>
       <c r="E17" t="n">
-        <v>-23.9286150564038</v>
+        <v>-28.1665669334067</v>
       </c>
       <c r="F17" t="n">
-        <v>0.285691448463723</v>
+        <v>0.381536838631078</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.119073063016372</v>
+        <v>-0.144372698646437</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00161998195318168</v>
+        <v>0.00228015145786663</v>
       </c>
       <c r="I17" t="n">
-        <v>98</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0000000032151860050683</v>
+        <v>-0.00000000287110789505956</v>
       </c>
       <c r="D18" t="n">
-        <v>0.000000000929497879865746</v>
+        <v>0.000000000232068845738583</v>
       </c>
       <c r="E18" t="n">
-        <v>-19.3165293475852</v>
+        <v>-21.975638509489</v>
       </c>
       <c r="F18" t="n">
-        <v>0.190710549440983</v>
+        <v>0.238732918197057</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.093332301387409</v>
+        <v>-0.108001931629995</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00102126338610707</v>
+        <v>0.00131351800505018</v>
       </c>
       <c r="I18" t="n">
-        <v>98</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.00000000214170459450046</v>
+        <v>-0.00000000182021027054008</v>
       </c>
       <c r="D19" t="n">
-        <v>0.000000000624174037887801</v>
+        <v>0.000000000146852331251988</v>
       </c>
       <c r="E19" t="n">
-        <v>-16.1925691927188</v>
+        <v>-18.0120336902386</v>
       </c>
       <c r="F19" t="n">
-        <v>0.136803551247869</v>
+        <v>0.163853621564138</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0767733162364369</v>
+        <v>-0.0863491897459432</v>
       </c>
       <c r="H19" t="n">
-        <v>0.000706261241767529</v>
+        <v>0.000859564182326996</v>
       </c>
       <c r="I19" t="n">
-        <v>98</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.00000000152126988823109</v>
+        <v>-0.00000000125729130997135</v>
       </c>
       <c r="D20" t="n">
-        <v>0.000000000442614365083958</v>
+        <v>0.000000000100967193306608</v>
       </c>
       <c r="E20" t="n">
-        <v>-13.9373464420318</v>
+        <v>-15.2593635143343</v>
       </c>
       <c r="F20" t="n">
-        <v>0.103091800728416</v>
+        <v>0.119616550477939</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0652153796755085</v>
+        <v>-0.071957936590277</v>
       </c>
       <c r="H20" t="n">
-        <v>0.000518793080148642</v>
+        <v>0.00060818545475409</v>
       </c>
       <c r="I20" t="n">
-        <v>98</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.00000000113284942497894</v>
+        <v>-0.000000000920636808726804</v>
       </c>
       <c r="D21" t="n">
-        <v>0.000000000327705935938465</v>
+        <v>0.00000000007355211036705</v>
       </c>
       <c r="E21" t="n">
-        <v>-12.2330235031243</v>
+        <v>-13.2367059370623</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0805149381710006</v>
+        <v>0.0912528040541048</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0566865396159357</v>
+        <v>-0.0616915886451893</v>
       </c>
       <c r="H21" t="n">
-        <v>0.000397582829778636</v>
+        <v>0.000453792025294844</v>
       </c>
       <c r="I21" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.000000000874942639156718</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.000000000251393004444739</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-10.9001650055631</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.0646591992257006</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-0.0501341691655996</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.000314661348782637</v>
-      </c>
-      <c r="I22" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.00000000520693650759922</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.00000000041839707087581</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-28.1665669334067</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.381536838631078</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-0.144372698646437</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.00228015145786663</v>
-      </c>
-      <c r="I23" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.00000000287110789505956</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.000000000232068845738583</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-21.975638509489</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.238732918197057</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-0.108001931629995</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.00131351800505018</v>
-      </c>
-      <c r="I24" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.00000000182021027054008</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.000000000146852331251988</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-18.0120336902386</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.163853621564138</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-0.0863491897459432</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.000859564182326996</v>
-      </c>
-      <c r="I25" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>19</v>
-      </c>
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.00000000125729130997135</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.000000000100967193306608</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-15.2593635143343</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.119616550477939</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-0.071957936590277</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.00060818545475409</v>
-      </c>
-      <c r="I26" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.000000000920636808726804</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.00000000007355211036705</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-13.2367059370623</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.0912528040541048</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-0.0616915886451893</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.000453792025294844</v>
-      </c>
-      <c r="I27" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>19</v>
-      </c>
-      <c r="B28" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-0.000000000703282836956543</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.0000000000559126332073573</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-11.6877331135838</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.071954425048699</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-0.0539955678872008</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.0003519313198679</v>
-      </c>
-      <c r="I28" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>19</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.000000000554760600150802</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.0000000000438897707791129</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-10.4630570845384</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.0582154526505852</v>
-      </c>
-      <c r="G29" t="n">
-        <v>-0.0480083212089503</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.000281077639206067</v>
-      </c>
-      <c r="I29" t="n">
         <v>117</v>
       </c>
     </row>
@@ -1284,103 +1046,103 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.00000000417591048371807</v>
+        <v>-0.000000005271362547422</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000000000398307320050934</v>
+        <v>0.000000000547806823275968</v>
       </c>
       <c r="D2" t="n">
-        <v>-15.1929611737021</v>
+        <v>-17.1463892336847</v>
       </c>
       <c r="E2" t="n">
-        <v>0.193564900779139</v>
+        <v>0.225187362237541</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0726169893876392</v>
+        <v>-0.0827340816894613</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00102434856808999</v>
+        <v>0.00120572797499709</v>
       </c>
       <c r="H2" t="n">
-        <v>889</v>
+        <v>635</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.00000000126569235111904</v>
+        <v>-0.00000000165532603721674</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000000000177298761385545</v>
+        <v>0.000000000232386765519311</v>
       </c>
       <c r="D3" t="n">
-        <v>-21.0933107994308</v>
+        <v>-24.541535486863</v>
       </c>
       <c r="E3" t="n">
-        <v>0.931934898902072</v>
+        <v>1.04974572349161</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.10612149296962</v>
+        <v>-0.125419152145658</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00551705757488237</v>
+        <v>0.00639621921866563</v>
       </c>
       <c r="H3" t="n">
-        <v>98</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.00000000347382807854553</v>
+        <v>-0.00000000446180089713661</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00000000047872682415761</v>
+        <v>0.000000000660065392455743</v>
       </c>
       <c r="D4" t="n">
-        <v>-18.2744293269652</v>
+        <v>-20.9575633560138</v>
       </c>
       <c r="E4" t="n">
-        <v>0.272957392084692</v>
+        <v>0.306271366882927</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0894267555167036</v>
+        <v>-0.103833315967078</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00153285479628087</v>
+        <v>0.0017616722643256</v>
       </c>
       <c r="H4" t="n">
-        <v>686</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.00000000190488946128634</v>
+        <v>-0.0000000024152365583794</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000000000091510691063535</v>
+        <v>0.000000000121062131176298</v>
       </c>
       <c r="D5" t="n">
-        <v>-16.971585540379</v>
+        <v>-19.3300617169062</v>
       </c>
       <c r="E5" t="n">
-        <v>0.216682394674058</v>
+        <v>0.241114077835117</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.082053890621999</v>
+        <v>-0.0944746690515683</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00118330245494271</v>
+        <v>0.00134422806719034</v>
       </c>
       <c r="H5" t="n">
-        <v>819</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>

--- a/Copper/6. Sensitivity analyses/Plots of HA SA/HA_Sensitivity_Summary.xlsx
+++ b/Copper/6. Sensitivity analyses/Plots of HA SA/HA_Sensitivity_Summary.xlsx
@@ -1,80 +1,87 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Copper/6. Sensitivity analyses/Plots of HA SA/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_A79D70068FBA1553F057F5993CC2F1A8C6DAC88D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD8F4E4F-C10B-44EC-8FBB-DA57DD9F0DCD}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="HA_Sensitivity_Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Overall_Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="HA_Sensitivity_Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Overall_Summary" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
-  <si>
-    <t xml:space="preserve">Typology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HA_transition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_delta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se_delta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_pct_change</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se_pct_change</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_log_rr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se_log_rr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30-40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40-50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50-60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NP Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD Tribs</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="18">
+  <si>
+    <t>Typology</t>
+  </si>
+  <si>
+    <t>HA_transition</t>
+  </si>
+  <si>
+    <t>mean_delta</t>
+  </si>
+  <si>
+    <t>se_delta</t>
+  </si>
+  <si>
+    <t>mean_pct_change</t>
+  </si>
+  <si>
+    <t>se_pct_change</t>
+  </si>
+  <si>
+    <t>mean_log_rr</t>
+  </si>
+  <si>
+    <t>se_log_rr</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>Main Stem</t>
+  </si>
+  <si>
+    <t>10-20</t>
+  </si>
+  <si>
+    <t>20-30</t>
+  </si>
+  <si>
+    <t>30-40</t>
+  </si>
+  <si>
+    <t>40-50</t>
+  </si>
+  <si>
+    <t>50-60</t>
+  </si>
+  <si>
+    <t>NP Tribs</t>
+  </si>
+  <si>
+    <t>P Tribs</t>
+  </si>
+  <si>
+    <t>PD Tribs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -110,6 +117,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -391,11 +407,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -424,598 +445,602 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="n">
-        <v>-0.0000000109260281521799</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.00000000217270477644284</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-24.0595479755571</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="C2">
+        <v>-1.09260281521799E-8</v>
+      </c>
+      <c r="D2">
+        <v>2.17270477644284E-9</v>
+      </c>
+      <c r="E2">
+        <v>-24.059547975557098</v>
+      </c>
+      <c r="F2">
         <v>0.519364390345745</v>
       </c>
-      <c r="G2" t="n">
-        <v>-0.120739395001742</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.00285424634346714</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="G2">
+        <v>-0.12073939500174199</v>
+      </c>
+      <c r="H2">
+        <v>2.8542463434671401E-3</v>
+      </c>
+      <c r="I2">
         <v>127</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="n">
-        <v>-0.00000000636789328771896</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.00000000122032261782168</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-19.3754605609599</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.373819701959428</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-0.0940960199525253</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.00194997087929842</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="C3">
+        <v>-6.3678932877189597E-9</v>
+      </c>
+      <c r="D3">
+        <v>1.2203226178216799E-9</v>
+      </c>
+      <c r="E3">
+        <v>-19.375460560959901</v>
+      </c>
+      <c r="F3">
+        <v>0.37381970195942799</v>
+      </c>
+      <c r="G3">
+        <v>-9.4096019952525298E-2</v>
+      </c>
+      <c r="H3">
+        <v>1.94997087929842E-3</v>
+      </c>
+      <c r="I3">
         <v>127</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="n">
-        <v>-0.00000000410881100036228</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.000000000751311807164492</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-16.1978038226263</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.283198707492642</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.0770460979615041</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.00142914584975396</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="C4">
+        <v>-4.1088110003622802E-9</v>
+      </c>
+      <c r="D4">
+        <v>7.5131180716449203E-10</v>
+      </c>
+      <c r="E4">
+        <v>-16.197803822626302</v>
+      </c>
+      <c r="F4">
+        <v>0.28319870749264198</v>
+      </c>
+      <c r="G4">
+        <v>-7.7046097961504106E-2</v>
+      </c>
+      <c r="H4">
+        <v>1.4291458497539601E-3</v>
+      </c>
+      <c r="I4">
         <v>127</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="n">
-        <v>-0.00000000285632198399075</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.000000000500145663040996</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="C5">
+        <v>-2.8563219839907499E-9</v>
+      </c>
+      <c r="D5">
+        <v>5.0014566304099601E-10</v>
+      </c>
+      <c r="E5">
         <v>-13.9104938183375</v>
       </c>
-      <c r="F5" t="n">
-        <v>0.22267357310752</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.0652273730983602</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.00109825262901874</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="F5">
+        <v>0.22267357310752001</v>
+      </c>
+      <c r="G5">
+        <v>-6.52273730983602E-2</v>
+      </c>
+      <c r="H5">
+        <v>1.09825262901874E-3</v>
+      </c>
+      <c r="I5">
         <v>127</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="n">
-        <v>-0.00000000209775831285812</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.000000000353876512371561</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="C6">
+        <v>-2.0977583128581201E-9</v>
+      </c>
+      <c r="D6">
+        <v>3.5387651237156097E-10</v>
+      </c>
+      <c r="E6">
         <v>-12.1886399909429</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>0.180179325270342</v>
       </c>
-      <c r="G6" t="n">
-        <v>-0.0565615224331752</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.000873919773102042</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="G6">
+        <v>-5.65615224331752E-2</v>
+      </c>
+      <c r="H6">
+        <v>8.7391977310204204E-4</v>
+      </c>
+      <c r="I6">
         <v>127</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>15</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
-      <c r="C7" t="n">
-        <v>-0.00000000431212662469429</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.000000000732510674399534</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-39.2443546078952</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="C7">
+        <v>-4.31212662469429E-9</v>
+      </c>
+      <c r="D7">
+        <v>7.3251067439953397E-10</v>
+      </c>
+      <c r="E7">
+        <v>-39.244354607895197</v>
+      </c>
+      <c r="F7">
         <v>0.908466087854785</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>-0.217024126734495</v>
       </c>
-      <c r="H7" t="n">
-        <v>0.00633693598334707</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="H7">
+        <v>6.3369359833470697E-3</v>
+      </c>
+      <c r="I7">
         <v>14</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>15</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="n">
-        <v>-0.00000000184125693789807</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.000000000298774498861813</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-28.1862503999904</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.481881337044835</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="C8">
+        <v>-1.8412569378980701E-9</v>
+      </c>
+      <c r="D8">
+        <v>2.98774498861813E-10</v>
+      </c>
+      <c r="E8">
+        <v>-28.186250399990399</v>
+      </c>
+      <c r="F8">
+        <v>0.48188133704483499</v>
+      </c>
+      <c r="G8">
         <v>-0.143917388131278</v>
       </c>
-      <c r="H8" t="n">
-        <v>0.00287786577037895</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="H8">
+        <v>2.8778657703789502E-3</v>
+      </c>
+      <c r="I8">
         <v>14</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>15</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="n">
-        <v>-0.00000000102224736035393</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.000000000162168698509139</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="C9">
+        <v>-1.02224736035393E-9</v>
+      </c>
+      <c r="D9">
+        <v>1.62168698509139E-10</v>
+      </c>
+      <c r="E9">
         <v>-21.9860667878466</v>
       </c>
-      <c r="F9" t="n">
-        <v>0.29777385282192</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="F9">
+        <v>0.29777385282191998</v>
+      </c>
+      <c r="G9">
         <v>-0.107868538314292</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.00164514860302336</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="H9">
+        <v>1.6451486030233599E-3</v>
+      </c>
+      <c r="I9">
         <v>14</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="C10" t="n">
-        <v>-0.000000000650526269084162</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.000000000101814451582528</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-18.0216151340535</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.202070243403988</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-0.0863176783693471</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.00106509249819166</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="C10">
+        <v>-6.5052626908416202E-10</v>
+      </c>
+      <c r="D10">
+        <v>1.01814451582528E-10</v>
+      </c>
+      <c r="E10">
+        <v>-18.021615134053501</v>
+      </c>
+      <c r="F10">
+        <v>0.20207024340398799</v>
+      </c>
+      <c r="G10">
+        <v>-8.6317678369347103E-2</v>
+      </c>
+      <c r="H10">
+        <v>1.0650924981916599E-3</v>
+      </c>
+      <c r="I10">
         <v>14</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" t="n">
-        <v>-0.000000000450472994053227</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.0000000000698706871238354</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-15.2693905045291</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.146161932400706</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-0.0719680291788789</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.000746457703950461</v>
-      </c>
-      <c r="I11" t="n">
+      <c r="C11">
+        <v>-4.5047299405322701E-10</v>
+      </c>
+      <c r="D11">
+        <v>6.9870687123835403E-11</v>
+      </c>
+      <c r="E11">
+        <v>-15.269390504529101</v>
+      </c>
+      <c r="F11">
+        <v>0.14616193240070599</v>
+      </c>
+      <c r="G11">
+        <v>-7.1968029178878901E-2</v>
+      </c>
+      <c r="H11">
+        <v>7.4645770395046103E-4</v>
+      </c>
+      <c r="I11">
         <v>14</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>16</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
       </c>
-      <c r="C12" t="n">
-        <v>-0.0000000101365266565971</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.00000000261414290126978</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-31.4127567413295</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.478777520088047</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-0.164772519519664</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.00300877299503251</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="C12">
+        <v>-1.01365266565971E-8</v>
+      </c>
+      <c r="D12">
+        <v>2.6141429012697801E-9</v>
+      </c>
+      <c r="E12">
+        <v>-31.412756741329499</v>
+      </c>
+      <c r="F12">
+        <v>0.47877752008804703</v>
+      </c>
+      <c r="G12">
+        <v>-0.16477251951966401</v>
+      </c>
+      <c r="H12">
+        <v>3.0087729950325102E-3</v>
+      </c>
+      <c r="I12">
         <v>98</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
       </c>
-      <c r="C13" t="n">
-        <v>-0.00000000529431734128614</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.00000000148290068883031</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="C13">
+        <v>-5.2943173412861398E-9</v>
+      </c>
+      <c r="D13">
+        <v>1.48290068883031E-9</v>
+      </c>
+      <c r="E13">
         <v>-23.9286150564038</v>
       </c>
-      <c r="F13" t="n">
-        <v>0.285691448463723</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-0.119073063016372</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.00161998195318168</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="F13">
+        <v>0.28569144846372302</v>
+      </c>
+      <c r="G13">
+        <v>-0.11907306301637199</v>
+      </c>
+      <c r="H13">
+        <v>1.61998195318168E-3</v>
+      </c>
+      <c r="I13">
         <v>98</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>16</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
-      <c r="C14" t="n">
-        <v>-0.0000000032151860050683</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.000000000929497879865746</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-19.3165293475852</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.190710549440983</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-0.093332301387409</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.00102126338610707</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="C14">
+        <v>-3.2151860050683001E-9</v>
+      </c>
+      <c r="D14">
+        <v>9.2949787986574601E-10</v>
+      </c>
+      <c r="E14">
+        <v>-19.316529347585199</v>
+      </c>
+      <c r="F14">
+        <v>0.19071054944098301</v>
+      </c>
+      <c r="G14">
+        <v>-9.3332301387409E-2</v>
+      </c>
+      <c r="H14">
+        <v>1.02126338610707E-3</v>
+      </c>
+      <c r="I14">
         <v>98</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
-      <c r="C15" t="n">
-        <v>-0.00000000214170459450046</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.000000000624174037887801</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="C15">
+        <v>-2.1417045945004599E-9</v>
+      </c>
+      <c r="D15">
+        <v>6.2417403788780096E-10</v>
+      </c>
+      <c r="E15">
         <v>-16.1925691927188</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>0.136803551247869</v>
       </c>
-      <c r="G15" t="n">
-        <v>-0.0767733162364369</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.000706261241767529</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="G15">
+        <v>-7.6773316236436906E-2</v>
+      </c>
+      <c r="H15">
+        <v>7.0626124176752898E-4</v>
+      </c>
+      <c r="I15">
         <v>98</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>16</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
       </c>
-      <c r="C16" t="n">
-        <v>-0.00000000152126988823109</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.000000000442614365083958</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-13.9373464420318</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.103091800728416</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-0.0652153796755085</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.000518793080148642</v>
-      </c>
-      <c r="I16" t="n">
+      <c r="C16">
+        <v>-1.52126988823109E-9</v>
+      </c>
+      <c r="D16">
+        <v>4.42614365083958E-10</v>
+      </c>
+      <c r="E16">
+        <v>-13.937346442031799</v>
+      </c>
+      <c r="F16">
+        <v>0.10309180072841601</v>
+      </c>
+      <c r="G16">
+        <v>-6.52153796755085E-2</v>
+      </c>
+      <c r="H16">
+        <v>5.1879308014864199E-4</v>
+      </c>
+      <c r="I16">
         <v>98</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
-      <c r="C17" t="n">
-        <v>-0.00000000520693650759922</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.00000000041839707087581</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-28.1665669334067</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.381536838631078</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-0.144372698646437</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.00228015145786663</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="C17">
+        <v>-5.2069365075992201E-9</v>
+      </c>
+      <c r="D17">
+        <v>4.1839707087580999E-10</v>
+      </c>
+      <c r="E17">
+        <v>-28.166566933406699</v>
+      </c>
+      <c r="F17">
+        <v>0.38153683863107801</v>
+      </c>
+      <c r="G17">
+        <v>-0.14437269864643701</v>
+      </c>
+      <c r="H17">
+        <v>2.2801514578666298E-3</v>
+      </c>
+      <c r="I17">
         <v>117</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>11</v>
       </c>
-      <c r="C18" t="n">
-        <v>-0.00000000287110789505956</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.000000000232068845738583</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-21.975638509489</v>
-      </c>
-      <c r="F18" t="n">
+      <c r="C18">
+        <v>-2.8711078950595602E-9</v>
+      </c>
+      <c r="D18">
+        <v>2.3206884573858301E-10</v>
+      </c>
+      <c r="E18">
+        <v>-21.975638509488999</v>
+      </c>
+      <c r="F18">
         <v>0.238732918197057</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>-0.108001931629995</v>
       </c>
-      <c r="H18" t="n">
-        <v>0.00131351800505018</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="H18">
+        <v>1.31351800505018E-3</v>
+      </c>
+      <c r="I18">
         <v>117</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
       </c>
-      <c r="C19" t="n">
-        <v>-0.00000000182021027054008</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.000000000146852331251988</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-18.0120336902386</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.163853621564138</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-0.0863491897459432</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.000859564182326996</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="C19">
+        <v>-1.8202102705400799E-9</v>
+      </c>
+      <c r="D19">
+        <v>1.4685233125198801E-10</v>
+      </c>
+      <c r="E19">
+        <v>-18.012033690238599</v>
+      </c>
+      <c r="F19">
+        <v>0.16385362156413799</v>
+      </c>
+      <c r="G19">
+        <v>-8.6349189745943203E-2</v>
+      </c>
+      <c r="H19">
+        <v>8.59564182326996E-4</v>
+      </c>
+      <c r="I19">
         <v>117</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>17</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
       </c>
-      <c r="C20" t="n">
-        <v>-0.00000000125729130997135</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.000000000100967193306608</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="C20">
+        <v>-1.2572913099713499E-9</v>
+      </c>
+      <c r="D20">
+        <v>1.00967193306608E-10</v>
+      </c>
+      <c r="E20">
         <v>-15.2593635143343</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>0.119616550477939</v>
       </c>
-      <c r="G20" t="n">
-        <v>-0.071957936590277</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.00060818545475409</v>
-      </c>
-      <c r="I20" t="n">
+      <c r="G20">
+        <v>-7.1957936590276994E-2</v>
+      </c>
+      <c r="H20">
+        <v>6.0818545475408998E-4</v>
+      </c>
+      <c r="I20">
         <v>117</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>17</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
       </c>
-      <c r="C21" t="n">
-        <v>-0.000000000920636808726804</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.00000000007355211036705</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="C21">
+        <v>-9.2063680872680401E-10</v>
+      </c>
+      <c r="D21">
+        <v>7.3552110367049995E-11</v>
+      </c>
+      <c r="E21">
         <v>-13.2367059370623</v>
       </c>
-      <c r="F21" t="n">
-        <v>0.0912528040541048</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-0.0616915886451893</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.000453792025294844</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="F21">
+        <v>9.1252804054104797E-2</v>
+      </c>
+      <c r="G21">
+        <v>-6.1691588645189303E-2</v>
+      </c>
+      <c r="H21">
+        <v>4.5379202529484397E-4</v>
+      </c>
+      <c r="I21">
         <v>117</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1041,112 +1066,112 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="n">
-        <v>-0.000000005271362547422</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.000000000547806823275968</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-17.1463892336847</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.225187362237541</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-0.0827340816894613</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.00120572797499709</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="B2">
+        <v>-5.2713625474220001E-9</v>
+      </c>
+      <c r="C2">
+        <v>5.4780682327596795E-10</v>
+      </c>
+      <c r="D2">
+        <v>-17.146389233684701</v>
+      </c>
+      <c r="E2">
+        <v>0.22518736223754099</v>
+      </c>
+      <c r="F2">
+        <v>-8.2734081689461295E-2</v>
+      </c>
+      <c r="G2">
+        <v>1.20572797499709E-3</v>
+      </c>
+      <c r="H2">
         <v>635</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="n">
-        <v>-0.00000000165532603721674</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.000000000232386765519311</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-24.541535486863</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.04974572349161</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-0.125419152145658</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.00639621921866563</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="B3">
+        <v>-1.6553260372167399E-9</v>
+      </c>
+      <c r="C3">
+        <v>2.3238676551931099E-10</v>
+      </c>
+      <c r="D3">
+        <v>-24.541535486863001</v>
+      </c>
+      <c r="E3">
+        <v>1.0497457234916101</v>
+      </c>
+      <c r="F3">
+        <v>-0.12541915214565799</v>
+      </c>
+      <c r="G3">
+        <v>6.3962192186656297E-3</v>
+      </c>
+      <c r="H3">
         <v>70</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="n">
-        <v>-0.00000000446180089713661</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.000000000660065392455743</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="B4">
+        <v>-4.46180089713661E-9</v>
+      </c>
+      <c r="C4">
+        <v>6.6006539245574302E-10</v>
+      </c>
+      <c r="D4">
         <v>-20.9575633560138</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0.306271366882927</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>-0.103833315967078</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.0017616722643256</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="G4">
+        <v>1.7616722643256E-3</v>
+      </c>
+      <c r="H4">
         <v>490</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="n">
-        <v>-0.0000000024152365583794</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.000000000121062131176298</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-19.3300617169062</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.241114077835117</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-0.0944746690515683</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.00134422806719034</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="B5">
+        <v>-2.4152365583794002E-9</v>
+      </c>
+      <c r="C5">
+        <v>1.21062131176298E-10</v>
+      </c>
+      <c r="D5">
+        <v>-19.330061716906201</v>
+      </c>
+      <c r="E5">
+        <v>0.24111407783511701</v>
+      </c>
+      <c r="F5">
+        <v>-9.4474669051568302E-2</v>
+      </c>
+      <c r="G5">
+        <v>1.3442280671903399E-3</v>
+      </c>
+      <c r="H5">
         <v>585</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>